--- a/artfynd/A 12519-2020 artfynd.xlsx
+++ b/artfynd/A 12519-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937318</v>
+        <v>119937316</v>
       </c>
       <c r="B2" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542922</v>
+        <v>542982</v>
       </c>
       <c r="R2" t="n">
-        <v>7020426</v>
+        <v>7020441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119937323</v>
+        <v>119937315</v>
       </c>
       <c r="B3" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542918</v>
+        <v>542998</v>
       </c>
       <c r="R3" t="n">
-        <v>7020503</v>
+        <v>7020424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937321</v>
+        <v>119937318</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542980</v>
+        <v>542922</v>
       </c>
       <c r="R6" t="n">
-        <v>7020470</v>
+        <v>7020426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119937316</v>
+        <v>119937323</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542982</v>
+        <v>542918</v>
       </c>
       <c r="R7" t="n">
-        <v>7020441</v>
+        <v>7020503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119937315</v>
+        <v>119937322</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542998</v>
+        <v>542980</v>
       </c>
       <c r="R8" t="n">
-        <v>7020424</v>
+        <v>7020470</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119937322</v>
+        <v>119937321</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>

--- a/artfynd/A 12519-2020 artfynd.xlsx
+++ b/artfynd/A 12519-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937316</v>
+        <v>119937315</v>
       </c>
       <c r="B2" t="n">
         <v>97907</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542982</v>
+        <v>542998</v>
       </c>
       <c r="R2" t="n">
-        <v>7020441</v>
+        <v>7020424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119937315</v>
+        <v>119937320</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542998</v>
+        <v>542927</v>
       </c>
       <c r="R3" t="n">
-        <v>7020424</v>
+        <v>7020445</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119937320</v>
+        <v>119937316</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542927</v>
+        <v>542982</v>
       </c>
       <c r="R4" t="n">
-        <v>7020445</v>
+        <v>7020441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119937317</v>
+        <v>119937322</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542978</v>
+        <v>542980</v>
       </c>
       <c r="R5" t="n">
-        <v>7020442</v>
+        <v>7020470</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937318</v>
+        <v>119937323</v>
       </c>
       <c r="B6" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542922</v>
+        <v>542918</v>
       </c>
       <c r="R6" t="n">
-        <v>7020426</v>
+        <v>7020503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119937323</v>
+        <v>119937317</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542918</v>
+        <v>542978</v>
       </c>
       <c r="R7" t="n">
-        <v>7020503</v>
+        <v>7020442</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119937322</v>
+        <v>119937321</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119937321</v>
+        <v>119937318</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542980</v>
+        <v>542922</v>
       </c>
       <c r="R9" t="n">
-        <v>7020470</v>
+        <v>7020426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 12519-2020 artfynd.xlsx
+++ b/artfynd/A 12519-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937315</v>
+        <v>119937320</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542998</v>
+        <v>542927</v>
       </c>
       <c r="R2" t="n">
-        <v>7020424</v>
+        <v>7020445</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119937320</v>
+        <v>119937322</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542927</v>
+        <v>542980</v>
       </c>
       <c r="R3" t="n">
-        <v>7020445</v>
+        <v>7020470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119937316</v>
+        <v>119937321</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542982</v>
+        <v>542980</v>
       </c>
       <c r="R4" t="n">
-        <v>7020441</v>
+        <v>7020470</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119937322</v>
+        <v>119937323</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542980</v>
+        <v>542918</v>
       </c>
       <c r="R5" t="n">
-        <v>7020470</v>
+        <v>7020503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937323</v>
+        <v>119937316</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542918</v>
+        <v>542982</v>
       </c>
       <c r="R6" t="n">
-        <v>7020503</v>
+        <v>7020441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119937317</v>
+        <v>119937315</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542978</v>
+        <v>542998</v>
       </c>
       <c r="R7" t="n">
-        <v>7020442</v>
+        <v>7020424</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119937321</v>
+        <v>119937318</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542980</v>
+        <v>542922</v>
       </c>
       <c r="R8" t="n">
-        <v>7020470</v>
+        <v>7020426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119937318</v>
+        <v>119937317</v>
       </c>
       <c r="B9" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542922</v>
+        <v>542978</v>
       </c>
       <c r="R9" t="n">
-        <v>7020426</v>
+        <v>7020442</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 12519-2020 artfynd.xlsx
+++ b/artfynd/A 12519-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937320</v>
+        <v>119937316</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542927</v>
+        <v>542982</v>
       </c>
       <c r="R2" t="n">
-        <v>7020445</v>
+        <v>7020441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119937322</v>
+        <v>119937318</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542980</v>
+        <v>542922</v>
       </c>
       <c r="R3" t="n">
-        <v>7020470</v>
+        <v>7020426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119937321</v>
+        <v>119937322</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,7 +984,7 @@
         <v>119937323</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937316</v>
+        <v>119937320</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542982</v>
+        <v>542927</v>
       </c>
       <c r="R6" t="n">
-        <v>7020441</v>
+        <v>7020445</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1188,7 @@
         <v>119937315</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119937318</v>
+        <v>119937321</v>
       </c>
       <c r="B8" t="n">
-        <v>78262</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542922</v>
+        <v>542980</v>
       </c>
       <c r="R8" t="n">
-        <v>7020426</v>
+        <v>7020470</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1392,7 @@
         <v>119937317</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 12519-2020 artfynd.xlsx
+++ b/artfynd/A 12519-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937316</v>
+        <v>119937318</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542982</v>
+        <v>542922</v>
       </c>
       <c r="R2" t="n">
-        <v>7020441</v>
+        <v>7020426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119937318</v>
+        <v>119937322</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542922</v>
+        <v>542980</v>
       </c>
       <c r="R3" t="n">
-        <v>7020426</v>
+        <v>7020470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119937322</v>
+        <v>119937321</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119937323</v>
+        <v>119937317</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542918</v>
+        <v>542978</v>
       </c>
       <c r="R5" t="n">
-        <v>7020503</v>
+        <v>7020442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937320</v>
+        <v>119937315</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542927</v>
+        <v>542998</v>
       </c>
       <c r="R6" t="n">
-        <v>7020445</v>
+        <v>7020424</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119937315</v>
+        <v>119937323</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542998</v>
+        <v>542918</v>
       </c>
       <c r="R7" t="n">
-        <v>7020424</v>
+        <v>7020503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119937321</v>
+        <v>119937320</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542980</v>
+        <v>542927</v>
       </c>
       <c r="R8" t="n">
-        <v>7020470</v>
+        <v>7020445</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119937317</v>
+        <v>119937316</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542978</v>
+        <v>542982</v>
       </c>
       <c r="R9" t="n">
-        <v>7020442</v>
+        <v>7020441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 12519-2020 artfynd.xlsx
+++ b/artfynd/A 12519-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937318</v>
+        <v>119937316</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542922</v>
+        <v>542982</v>
       </c>
       <c r="R2" t="n">
-        <v>7020426</v>
+        <v>7020441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119937322</v>
+        <v>119937318</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542980</v>
+        <v>542922</v>
       </c>
       <c r="R3" t="n">
-        <v>7020470</v>
+        <v>7020426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119937321</v>
+        <v>119937323</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542980</v>
+        <v>542918</v>
       </c>
       <c r="R4" t="n">
-        <v>7020470</v>
+        <v>7020503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937315</v>
+        <v>119937320</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542998</v>
+        <v>542927</v>
       </c>
       <c r="R6" t="n">
-        <v>7020424</v>
+        <v>7020445</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119937323</v>
+        <v>119937321</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542918</v>
+        <v>542980</v>
       </c>
       <c r="R7" t="n">
-        <v>7020503</v>
+        <v>7020470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119937320</v>
+        <v>119937322</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542927</v>
+        <v>542980</v>
       </c>
       <c r="R8" t="n">
-        <v>7020445</v>
+        <v>7020470</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119937316</v>
+        <v>119937315</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542982</v>
+        <v>542998</v>
       </c>
       <c r="R9" t="n">
-        <v>7020441</v>
+        <v>7020424</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 12519-2020 artfynd.xlsx
+++ b/artfynd/A 12519-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937316</v>
+        <v>119937318</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542982</v>
+        <v>542922</v>
       </c>
       <c r="R2" t="n">
-        <v>7020441</v>
+        <v>7020426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119937318</v>
+        <v>119937321</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542922</v>
+        <v>542980</v>
       </c>
       <c r="R3" t="n">
-        <v>7020426</v>
+        <v>7020470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119937323</v>
+        <v>119937317</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542918</v>
+        <v>542978</v>
       </c>
       <c r="R4" t="n">
-        <v>7020503</v>
+        <v>7020442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119937317</v>
+        <v>119937315</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542978</v>
+        <v>542998</v>
       </c>
       <c r="R5" t="n">
-        <v>7020442</v>
+        <v>7020424</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937320</v>
+        <v>119937323</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542927</v>
+        <v>542918</v>
       </c>
       <c r="R6" t="n">
-        <v>7020445</v>
+        <v>7020503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119937321</v>
+        <v>119937322</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119937322</v>
+        <v>119937316</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542980</v>
+        <v>542982</v>
       </c>
       <c r="R8" t="n">
-        <v>7020470</v>
+        <v>7020441</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119937315</v>
+        <v>119937320</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542998</v>
+        <v>542927</v>
       </c>
       <c r="R9" t="n">
-        <v>7020424</v>
+        <v>7020445</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 12519-2020 artfynd.xlsx
+++ b/artfynd/A 12519-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937318</v>
+        <v>119937321</v>
       </c>
       <c r="B2" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542922</v>
+        <v>542980</v>
       </c>
       <c r="R2" t="n">
-        <v>7020426</v>
+        <v>7020470</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119937321</v>
+        <v>119937317</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542980</v>
+        <v>542978</v>
       </c>
       <c r="R3" t="n">
-        <v>7020470</v>
+        <v>7020442</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119937317</v>
+        <v>119937323</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542978</v>
+        <v>542918</v>
       </c>
       <c r="R4" t="n">
-        <v>7020442</v>
+        <v>7020503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119937315</v>
+        <v>119937316</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542998</v>
+        <v>542982</v>
       </c>
       <c r="R5" t="n">
-        <v>7020424</v>
+        <v>7020441</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937323</v>
+        <v>119937315</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542918</v>
+        <v>542998</v>
       </c>
       <c r="R6" t="n">
-        <v>7020503</v>
+        <v>7020424</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119937316</v>
+        <v>119937320</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542982</v>
+        <v>542927</v>
       </c>
       <c r="R8" t="n">
-        <v>7020441</v>
+        <v>7020445</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119937320</v>
+        <v>119937318</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542927</v>
+        <v>542922</v>
       </c>
       <c r="R9" t="n">
-        <v>7020445</v>
+        <v>7020426</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 12519-2020 artfynd.xlsx
+++ b/artfynd/A 12519-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937321</v>
+        <v>119937316</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542980</v>
+        <v>542982</v>
       </c>
       <c r="R2" t="n">
-        <v>7020470</v>
+        <v>7020441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119937317</v>
+        <v>119937321</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542978</v>
+        <v>542980</v>
       </c>
       <c r="R3" t="n">
-        <v>7020442</v>
+        <v>7020470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119937323</v>
+        <v>119937317</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542918</v>
+        <v>542978</v>
       </c>
       <c r="R4" t="n">
-        <v>7020503</v>
+        <v>7020442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119937316</v>
+        <v>119937323</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542982</v>
+        <v>542918</v>
       </c>
       <c r="R5" t="n">
-        <v>7020441</v>
+        <v>7020503</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937315</v>
+        <v>119937322</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542998</v>
+        <v>542980</v>
       </c>
       <c r="R6" t="n">
-        <v>7020424</v>
+        <v>7020470</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119937322</v>
+        <v>119937318</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542980</v>
+        <v>542922</v>
       </c>
       <c r="R7" t="n">
-        <v>7020470</v>
+        <v>7020426</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119937318</v>
+        <v>119937315</v>
       </c>
       <c r="B9" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542922</v>
+        <v>542998</v>
       </c>
       <c r="R9" t="n">
-        <v>7020426</v>
+        <v>7020424</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 12519-2020 artfynd.xlsx
+++ b/artfynd/A 12519-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119937316</v>
+        <v>119937315</v>
       </c>
       <c r="B2" t="n">
         <v>97930</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542982</v>
+        <v>542998</v>
       </c>
       <c r="R2" t="n">
-        <v>7020441</v>
+        <v>7020424</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119937321</v>
+        <v>119937323</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542980</v>
+        <v>542918</v>
       </c>
       <c r="R3" t="n">
-        <v>7020470</v>
+        <v>7020503</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119937317</v>
+        <v>119937316</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542978</v>
+        <v>542982</v>
       </c>
       <c r="R4" t="n">
-        <v>7020442</v>
+        <v>7020441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119937323</v>
+        <v>119937320</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>542918</v>
+        <v>542927</v>
       </c>
       <c r="R5" t="n">
-        <v>7020503</v>
+        <v>7020445</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119937322</v>
+        <v>119937321</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119937318</v>
+        <v>119937322</v>
       </c>
       <c r="B7" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>542922</v>
+        <v>542980</v>
       </c>
       <c r="R7" t="n">
-        <v>7020426</v>
+        <v>7020470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119937320</v>
+        <v>119937318</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542927</v>
+        <v>542922</v>
       </c>
       <c r="R8" t="n">
-        <v>7020445</v>
+        <v>7020426</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119937315</v>
+        <v>119937317</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542998</v>
+        <v>542978</v>
       </c>
       <c r="R9" t="n">
-        <v>7020424</v>
+        <v>7020442</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
